--- a/docs/example/invoice-export.xlsx
+++ b/docs/example/invoice-export.xlsx
@@ -94,15 +94,15 @@
   </numFmts>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
     <font>
-      <family val="2"/>
       <b val="1"/>
       <color/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">

--- a/docs/example/invoice-export.xlsx
+++ b/docs/example/invoice-export.xlsx
@@ -58,10 +58,10 @@
     <t>Q-00001/GNS/X/2026</t>
   </si>
   <si>
-    <t>2026-10-10</t>
-  </si>
-  <si>
-    <t>2026-11-09</t>
+    <t>2026-10-11</t>
+  </si>
+  <si>
+    <t>2026-11-10</t>
   </si>
   <si>
     <t>PT Samudra Contoh Nusantara</t>

--- a/docs/example/invoice-export.xlsx
+++ b/docs/example/invoice-export.xlsx
@@ -125,13 +125,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
-      <alignment/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="false">
-      <alignment/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -441,40 +444,40 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="3">
         <v>19560420</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="2" t="s">
         <v>22</v>
       </c>
     </row>

--- a/docs/example/invoice-export.xlsx
+++ b/docs/example/invoice-export.xlsx
@@ -58,10 +58,10 @@
     <t>Q-00001/GNS/X/2026</t>
   </si>
   <si>
-    <t>2026-10-11</t>
-  </si>
-  <si>
-    <t>2026-11-10</t>
+    <t>2026-10-12</t>
+  </si>
+  <si>
+    <t>2026-11-11</t>
   </si>
   <si>
     <t>PT Samudra Contoh Nusantara</t>
